--- a/invoices.xlsx
+++ b/invoices.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="11">
   <si>
     <t>Invoice No</t>
   </si>
@@ -34,6 +34,9 @@
     <t>INV-20260403130312</t>
   </si>
   <si>
+    <t>INV-20260403131506</t>
+  </si>
+  <si>
     <t>fleetgaurd</t>
   </si>
   <si>
@@ -41,6 +44,9 @@
   </si>
   <si>
     <t>INV-20260403130312.pdf</t>
+  </si>
+  <si>
+    <t>INV-20260403131506.pdf</t>
   </si>
 </sst>
 </file>
@@ -372,7 +378,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -397,16 +403,33 @@
         <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C2">
         <v>59000</v>
       </c>
       <c r="D2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" t="s">
         <v>7</v>
       </c>
-      <c r="E2" t="s">
+      <c r="C3">
+        <v>590472</v>
+      </c>
+      <c r="D3" t="s">
         <v>8</v>
+      </c>
+      <c r="E3" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/invoices.xlsx
+++ b/invoices.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="13">
   <si>
     <t>Invoice No</t>
   </si>
@@ -37,6 +37,9 @@
     <t>INV-20260403131506</t>
   </si>
   <si>
+    <t>INV-20260403154223</t>
+  </si>
+  <si>
     <t>fleetgaurd</t>
   </si>
   <si>
@@ -47,6 +50,9 @@
   </si>
   <si>
     <t>INV-20260403131506.pdf</t>
+  </si>
+  <si>
+    <t>static/invoices/INV-20260403154223.pdf</t>
   </si>
 </sst>
 </file>
@@ -378,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -403,16 +409,16 @@
         <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C2">
         <v>59000</v>
       </c>
       <c r="D2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -420,16 +426,33 @@
         <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C3">
         <v>590472</v>
       </c>
       <c r="D3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" t="s">
         <v>8</v>
       </c>
-      <c r="E3" t="s">
-        <v>10</v>
+      <c r="C4">
+        <v>160.48</v>
+      </c>
+      <c r="D4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/invoices.xlsx
+++ b/invoices.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="16">
   <si>
     <t>Invoice No</t>
   </si>
@@ -40,9 +40,15 @@
     <t>INV-20260403154223</t>
   </si>
   <si>
+    <t>INV-20260403154224</t>
+  </si>
+  <si>
     <t>fleetgaurd</t>
   </si>
   <si>
+    <t>radiance polymers</t>
+  </si>
+  <si>
     <t>03-04-2026</t>
   </si>
   <si>
@@ -53,6 +59,9 @@
   </si>
   <si>
     <t>static/invoices/INV-20260403154223.pdf</t>
+  </si>
+  <si>
+    <t>INV-20260403154224.pdf</t>
   </si>
 </sst>
 </file>
@@ -384,7 +393,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -409,16 +418,16 @@
         <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C2">
         <v>59000</v>
       </c>
       <c r="D2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -426,16 +435,16 @@
         <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C3">
         <v>590472</v>
       </c>
       <c r="D3" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -443,16 +452,33 @@
         <v>7</v>
       </c>
       <c r="B4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C4">
         <v>160.48</v>
       </c>
       <c r="D4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E4" t="s">
-        <v>12</v>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5">
+        <v>708</v>
+      </c>
+      <c r="D5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/invoices.xlsx
+++ b/invoices.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="18">
   <si>
     <t>Invoice No</t>
   </si>
@@ -43,6 +43,9 @@
     <t>INV-20260403154224</t>
   </si>
   <si>
+    <t>INV-20260403154225</t>
+  </si>
+  <si>
     <t>fleetgaurd</t>
   </si>
   <si>
@@ -62,6 +65,9 @@
   </si>
   <si>
     <t>INV-20260403154224.pdf</t>
+  </si>
+  <si>
+    <t>INV-20260403154225.pdf</t>
   </si>
 </sst>
 </file>
@@ -393,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -418,16 +424,16 @@
         <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C2">
         <v>59000</v>
       </c>
       <c r="D2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -435,16 +441,16 @@
         <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C3">
         <v>590472</v>
       </c>
       <c r="D3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -452,16 +458,16 @@
         <v>7</v>
       </c>
       <c r="B4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C4">
         <v>160.48</v>
       </c>
       <c r="D4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -469,16 +475,33 @@
         <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C5">
         <v>708</v>
       </c>
       <c r="D5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" t="s">
         <v>11</v>
       </c>
-      <c r="E5" t="s">
-        <v>15</v>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
